--- a/Result/profitability/3438.xlsx
+++ b/Result/profitability/3438.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4125</v>
+        <v>0.42</v>
       </c>
       <c r="N2" t="n">
-        <v>35.62875</v>
+        <v>35.6375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="N3" t="n">
-        <v>35.8675</v>
+        <v>36.3925</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.56</v>
       </c>
       <c r="M4" t="n">
-        <v>0.91875</v>
+        <v>0.92625</v>
       </c>
       <c r="N4" t="n">
-        <v>36.7075</v>
+        <v>37.22125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9537499999999999</v>
+        <v>1.02625</v>
       </c>
       <c r="N5" t="n">
-        <v>37.6375</v>
+        <v>38.3325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01375</v>
+        <v>1.00875</v>
       </c>
       <c r="N6" t="n">
-        <v>38.1025</v>
+        <v>38.945</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.76</v>
       </c>
       <c r="M7" t="n">
-        <v>1.055</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>38.935</v>
+        <v>38.9375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16125</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>39.0275</v>
+        <v>38.96125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>38.89124999999999</v>
+        <v>38.89125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9924999999999999</v>
+        <v>0.9925</v>
       </c>
       <c r="N12" t="n">
         <v>38.2075</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>250</v>
+      </c>
+      <c r="D75" t="n">
+        <v>155</v>
+      </c>
+      <c r="E75" t="n">
+        <v>95</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.61875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6250000000000002</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5300000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01370571502456686</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.052631578947369</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.560000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1706568446899939</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
